--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486999_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486999_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>E. STOILOV</t>
+          <t>D. DE LA RUA DE AGUSTIN</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>10.5191</v>
+        <v>10.2993</v>
       </c>
       <c r="E2" t="n">
-        <v>4.4803</v>
+        <v>6.5979</v>
       </c>
       <c r="F2" t="n">
-        <v>6.0388</v>
+        <v>3.7014</v>
       </c>
       <c r="G2" t="n">
-        <v>4.153</v>
+        <v>6.5161</v>
       </c>
       <c r="H2" t="n">
-        <v>3.9871</v>
+        <v>4.214</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1659</v>
+        <v>2.302</v>
       </c>
       <c r="J2" t="n">
-        <v>3.1814</v>
+        <v>5.71</v>
       </c>
       <c r="K2" t="n">
-        <v>3.063</v>
+        <v>4.0134</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1184</v>
+        <v>1.6967</v>
       </c>
       <c r="M2" t="n">
-        <v>0.9716</v>
+        <v>0.8061</v>
       </c>
       <c r="N2" t="n">
-        <v>0.9241</v>
+        <v>0.2007</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0475</v>
+        <v>0.6054</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.8214</v>
+        <v>1.8481</v>
       </c>
       <c r="Q2" t="n">
-        <v>-3.0801</v>
+        <v>-1.0267</v>
       </c>
       <c r="R2" t="n">
-        <v>2.2588</v>
+        <v>2.8748</v>
       </c>
       <c r="S2" t="n">
-        <v>4.4812</v>
+        <v>0.7565</v>
       </c>
       <c r="T2" t="n">
-        <v>2.1307</v>
+        <v>0.736</v>
       </c>
       <c r="U2" t="n">
-        <v>2.3505</v>
+        <v>0.0205</v>
       </c>
       <c r="V2" t="n">
-        <v>2.7063</v>
+        <v>1.1786</v>
       </c>
       <c r="W2" t="n">
-        <v>2.2484</v>
+        <v>1.1786</v>
       </c>
       <c r="X2" t="n">
-        <v>0.4579</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D. DE LA RUA DE AGUSTIN</t>
+          <t>E. STOILOV</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>8.7575</v>
+        <v>8.684200000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>5.1451</v>
+        <v>3.3568</v>
       </c>
       <c r="F3" t="n">
-        <v>3.6124</v>
+        <v>5.3274</v>
       </c>
       <c r="G3" t="n">
-        <v>6.5161</v>
+        <v>4.153</v>
       </c>
       <c r="H3" t="n">
-        <v>4.214</v>
+        <v>3.9871</v>
       </c>
       <c r="I3" t="n">
-        <v>2.302</v>
+        <v>0.1659</v>
       </c>
       <c r="J3" t="n">
-        <v>5.71</v>
+        <v>3.1814</v>
       </c>
       <c r="K3" t="n">
-        <v>4.0134</v>
+        <v>3.063</v>
       </c>
       <c r="L3" t="n">
-        <v>1.6967</v>
+        <v>0.1184</v>
       </c>
       <c r="M3" t="n">
-        <v>0.8061</v>
+        <v>0.9716</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2007</v>
+        <v>0.9241</v>
       </c>
       <c r="O3" t="n">
-        <v>0.6054</v>
+        <v>0.0475</v>
       </c>
       <c r="P3" t="n">
-        <v>1.8481</v>
+        <v>-0.8214</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.0267</v>
+        <v>-3.0801</v>
       </c>
       <c r="R3" t="n">
-        <v>2.8748</v>
+        <v>2.2588</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.7853</v>
+        <v>2.6463</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.7169</v>
+        <v>1.0072</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0684</v>
+        <v>1.6391</v>
       </c>
       <c r="V3" t="n">
-        <v>1.1786</v>
+        <v>2.7063</v>
       </c>
       <c r="W3" t="n">
-        <v>1.1786</v>
+        <v>2.2484</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>0.4579</v>
       </c>
     </row>
     <row r="4">
@@ -721,10 +721,10 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.2722</v>
+        <v>4.3768</v>
       </c>
       <c r="E4" t="n">
-        <v>2.6295</v>
+        <v>2.7341</v>
       </c>
       <c r="F4" t="n">
         <v>1.6427</v>
@@ -766,10 +766,10 @@
         <v>0.616</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1976</v>
+        <v>0.3022</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1317</v>
+        <v>-0.0271</v>
       </c>
       <c r="U4" t="n">
         <v>0.3294</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.9628</v>
+        <v>3.1605</v>
       </c>
       <c r="E5" t="n">
-        <v>1.2898</v>
+        <v>0.3097</v>
       </c>
       <c r="F5" t="n">
-        <v>2.6729</v>
+        <v>2.8508</v>
       </c>
       <c r="G5" t="n">
         <v>-0.3446</v>
@@ -844,13 +844,13 @@
         <v>2.0534</v>
       </c>
       <c r="S5" t="n">
-        <v>2.1021</v>
+        <v>1.2998</v>
       </c>
       <c r="T5" t="n">
-        <v>2.0725</v>
+        <v>1.0924</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0295</v>
+        <v>0.2074</v>
       </c>
       <c r="V5" t="n">
         <v>1.1786</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.7912</v>
+        <v>3.0631</v>
       </c>
       <c r="E6" t="n">
-        <v>1.7257</v>
+        <v>2.3533</v>
       </c>
       <c r="F6" t="n">
-        <v>1.0655</v>
+        <v>0.7098</v>
       </c>
       <c r="G6" t="n">
         <v>1.0445</v>
@@ -922,13 +922,13 @@
         <v>0.8214</v>
       </c>
       <c r="S6" t="n">
-        <v>0.6851</v>
+        <v>0.957</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3952</v>
+        <v>0.2324</v>
       </c>
       <c r="U6" t="n">
-        <v>1.0803</v>
+        <v>0.7246</v>
       </c>
       <c r="V6" t="n">
         <v>0.2402</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>N. ZIZIC</t>
+          <t>J. RODRIGUEZ JIMENEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.6393</v>
+        <v>2.7495</v>
       </c>
       <c r="E7" t="n">
-        <v>2.3267</v>
+        <v>1.6863</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3125</v>
+        <v>1.0632</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4461</v>
+        <v>1.4845</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.7459</v>
+        <v>0.3373</v>
       </c>
       <c r="I7" t="n">
-        <v>1.192</v>
+        <v>1.1472</v>
       </c>
       <c r="J7" t="n">
-        <v>1.1689</v>
+        <v>1.5972</v>
       </c>
       <c r="K7" t="n">
-        <v>0.419</v>
+        <v>0.3343</v>
       </c>
       <c r="L7" t="n">
-        <v>0.7498</v>
+        <v>1.2629</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.7228</v>
+        <v>-0.1127</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.1649</v>
+        <v>0.003</v>
       </c>
       <c r="O7" t="n">
-        <v>0.4422</v>
+        <v>-0.1157</v>
       </c>
       <c r="P7" t="n">
-        <v>1.6427</v>
+        <v>1.0267</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.6427</v>
+        <v>1.0267</v>
       </c>
       <c r="S7" t="n">
-        <v>0.8995</v>
+        <v>0.2383</v>
       </c>
       <c r="T7" t="n">
-        <v>1.5069</v>
+        <v>0.0891</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.6074000000000001</v>
+        <v>0.1492</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.3491</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.3491</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. RODRIGUEZ JIMENEZ</t>
+          <t>N. ZIZIC</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>2.2718</v>
+        <v>2.2414</v>
       </c>
       <c r="E8" t="n">
-        <v>1.2679</v>
+        <v>1.8696</v>
       </c>
       <c r="F8" t="n">
-        <v>1.0039</v>
+        <v>0.3718</v>
       </c>
       <c r="G8" t="n">
-        <v>1.4845</v>
+        <v>0.4461</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3373</v>
+        <v>-0.7459</v>
       </c>
       <c r="I8" t="n">
-        <v>1.1472</v>
+        <v>1.192</v>
       </c>
       <c r="J8" t="n">
-        <v>1.5972</v>
+        <v>1.1689</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3343</v>
+        <v>0.419</v>
       </c>
       <c r="L8" t="n">
-        <v>1.2629</v>
+        <v>0.7498</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.1127</v>
+        <v>-0.7228</v>
       </c>
       <c r="N8" t="n">
-        <v>0.003</v>
+        <v>-1.1649</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.1157</v>
+        <v>0.4422</v>
       </c>
       <c r="P8" t="n">
-        <v>1.0267</v>
+        <v>1.6427</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.0267</v>
+        <v>1.6427</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2394</v>
+        <v>0.5017</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3294</v>
+        <v>1.0498</v>
       </c>
       <c r="U8" t="n">
-        <v>0.08989999999999999</v>
+        <v>-0.5481</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-0.3491</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>-0.3491</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>R. GOMEZ BARRAL</t>
+          <t>K. JOHNSON</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.375</v>
+        <v>1.7576</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.0046</v>
+        <v>-0.8260999999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>1.3797</v>
+        <v>2.5837</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.0344</v>
+        <v>2.6518</v>
       </c>
       <c r="H9" t="n">
-        <v>0.4182</v>
+        <v>1.0126</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.4526</v>
+        <v>1.6392</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.1745</v>
+        <v>1.5645</v>
       </c>
       <c r="K9" t="n">
-        <v>0.7202</v>
+        <v>0.3675</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.8947</v>
+        <v>1.197</v>
       </c>
       <c r="M9" t="n">
-        <v>0.1401</v>
+        <v>1.0873</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.302</v>
+        <v>0.6452</v>
       </c>
       <c r="O9" t="n">
         <v>0.4422</v>
       </c>
       <c r="P9" t="n">
-        <v>0.4107</v>
+        <v>-0.616</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.0267</v>
+        <v>-3.0801</v>
       </c>
       <c r="R9" t="n">
-        <v>1.4374</v>
+        <v>2.4641</v>
       </c>
       <c r="S9" t="n">
-        <v>1.9987</v>
+        <v>1.4897</v>
       </c>
       <c r="T9" t="n">
-        <v>2.1966</v>
+        <v>0.6895</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1979</v>
+        <v>0.8002</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-1.7679</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.7679</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>K. JOHNSON</t>
+          <t>J. SOLARIN</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>1.3713</v>
+        <v>1.5065</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.2717</v>
+        <v>0.5093</v>
       </c>
       <c r="F10" t="n">
-        <v>2.643</v>
+        <v>0.9972</v>
       </c>
       <c r="G10" t="n">
-        <v>2.6518</v>
+        <v>-0.5877</v>
       </c>
       <c r="H10" t="n">
-        <v>1.0126</v>
+        <v>0.8595</v>
       </c>
       <c r="I10" t="n">
-        <v>1.6392</v>
+        <v>-1.4472</v>
       </c>
       <c r="J10" t="n">
-        <v>1.5645</v>
+        <v>-0.2228</v>
       </c>
       <c r="K10" t="n">
-        <v>0.3675</v>
+        <v>1.1324</v>
       </c>
       <c r="L10" t="n">
-        <v>1.197</v>
+        <v>-1.3552</v>
       </c>
       <c r="M10" t="n">
-        <v>1.0873</v>
+        <v>-0.3649</v>
       </c>
       <c r="N10" t="n">
-        <v>0.6452</v>
+        <v>-0.2729</v>
       </c>
       <c r="O10" t="n">
-        <v>0.4422</v>
+        <v>-0.092</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.616</v>
+        <v>2.4641</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.0801</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
         <v>2.4641</v>
       </c>
       <c r="S10" t="n">
-        <v>1.1035</v>
+        <v>0.8088</v>
       </c>
       <c r="T10" t="n">
-        <v>0.244</v>
+        <v>0.7321</v>
       </c>
       <c r="U10" t="n">
-        <v>0.8595</v>
+        <v>0.0766</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.7679</v>
+        <v>-1.1786</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.7679</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. SOLARIN</t>
+          <t>G. GANTT</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>1.3172</v>
+        <v>0.7437</v>
       </c>
       <c r="E11" t="n">
-        <v>0.5868</v>
+        <v>0.2978</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7304</v>
+        <v>0.4459</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.5877</v>
+        <v>-0.8942</v>
       </c>
       <c r="H11" t="n">
-        <v>0.8595</v>
+        <v>-0.5386</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.4472</v>
+        <v>-0.3556</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.2228</v>
+        <v>-0.2212</v>
       </c>
       <c r="K11" t="n">
-        <v>1.1324</v>
+        <v>0.0423</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.3552</v>
+        <v>-0.2636</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.3649</v>
+        <v>-0.6729000000000001</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.2729</v>
+        <v>-0.581</v>
       </c>
       <c r="O11" t="n">
         <v>-0.092</v>
       </c>
       <c r="P11" t="n">
-        <v>2.4641</v>
+        <v>0.8214</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2.4641</v>
+        <v>0.8214</v>
       </c>
       <c r="S11" t="n">
-        <v>0.6194</v>
+        <v>0.8165</v>
       </c>
       <c r="T11" t="n">
-        <v>0.8096</v>
+        <v>0.5191</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1901</v>
+        <v>0.2974</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.1786</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.1786</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>G. GANTT</t>
+          <t>R. GOMEZ BARRAL</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,58 +1345,58 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.5164</v>
+        <v>0.2606</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.8141</v>
+        <v>-1.0894</v>
       </c>
       <c r="F12" t="n">
-        <v>0.2977</v>
+        <v>1.35</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.8942</v>
+        <v>-1.0344</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.5386</v>
+        <v>0.4182</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.3556</v>
+        <v>-1.4526</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.2212</v>
+        <v>-1.1745</v>
       </c>
       <c r="K12" t="n">
-        <v>0.0423</v>
+        <v>0.7202</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.2636</v>
+        <v>-1.8947</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.6729000000000001</v>
+        <v>0.1401</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.581</v>
+        <v>-0.302</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.092</v>
+        <v>0.4422</v>
       </c>
       <c r="P12" t="n">
-        <v>0.8214</v>
+        <v>0.4107</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>-1.0267</v>
       </c>
       <c r="R12" t="n">
-        <v>0.8214</v>
+        <v>1.4374</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.4436</v>
+        <v>0.8843</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5928</v>
+        <v>1.1118</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1492</v>
+        <v>-0.2275</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.9397</v>
+        <v>-0.0338</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.2061</v>
+        <v>-0.6559</v>
       </c>
       <c r="F13" t="n">
-        <v>0.2664</v>
+        <v>0.6221</v>
       </c>
       <c r="G13" t="n">
         <v>-1.0838</v>
@@ -1468,13 +1468,13 @@
         <v>1.0267</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.6424</v>
+        <v>0.2635</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.4611</v>
+        <v>0.0891</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1813</v>
+        <v>0.1744</v>
       </c>
       <c r="V13" t="n">
         <v>-0.2402</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>37.8213</v>
+        <v>38.8094</v>
       </c>
       <c r="E14" t="n">
-        <v>16.1553</v>
+        <v>17.1434</v>
       </c>
       <c r="F14" t="n">
-        <v>21.6659</v>
+        <v>21.666</v>
       </c>
       <c r="G14" t="n">
         <v>15.8099</v>
@@ -1516,7 +1516,7 @@
         <v>14.8903</v>
       </c>
       <c r="I14" t="n">
-        <v>0.9196000000000002</v>
+        <v>0.9196000000000011</v>
       </c>
       <c r="J14" t="n">
         <v>14.5658</v>
@@ -1546,10 +1546,10 @@
         <v>19.5075</v>
       </c>
       <c r="S14" t="n">
-        <v>9.976400000000002</v>
+        <v>10.9646</v>
       </c>
       <c r="T14" t="n">
-        <v>6.3332</v>
+        <v>7.321400000000001</v>
       </c>
       <c r="U14" t="n">
         <v>3.6432</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>P. ARRIBAS GOMEZ</t>
+          <t>M. ALVAREZ PUERTAS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,58 +1579,58 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.323</v>
+        <v>0.4005</v>
       </c>
       <c r="E15" t="n">
-        <v>0.7173</v>
+        <v>0.7209</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.3943</v>
+        <v>-0.3203</v>
       </c>
       <c r="G15" t="n">
-        <v>0.5547</v>
+        <v>0.5216</v>
       </c>
       <c r="H15" t="n">
-        <v>0.1363</v>
+        <v>-0.7493</v>
       </c>
       <c r="I15" t="n">
-        <v>0.4184</v>
+        <v>1.2709</v>
       </c>
       <c r="J15" t="n">
-        <v>0.9149</v>
+        <v>0.8604000000000001</v>
       </c>
       <c r="K15" t="n">
-        <v>0.9149</v>
+        <v>-0.363</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.2234</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.3602</v>
+        <v>-0.3388</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.7786</v>
+        <v>-0.3863</v>
       </c>
       <c r="O15" t="n">
-        <v>0.4184</v>
+        <v>0.0475</v>
       </c>
       <c r="P15" t="n">
-        <v>0.2053</v>
+        <v>0.616</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0.2053</v>
+        <v>0.616</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.437</v>
+        <v>-0.7371</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1976</v>
+        <v>-0.1396</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2394</v>
+        <v>-0.5975</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. ALVAREZ PUERTAS</t>
+          <t>P. ARRIBAS GOMEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,58 +1657,58 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0571</v>
+        <v>0.3823</v>
       </c>
       <c r="E16" t="n">
-        <v>0.407</v>
+        <v>0.7173</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.35</v>
+        <v>-0.335</v>
       </c>
       <c r="G16" t="n">
-        <v>0.5216</v>
+        <v>0.5547</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.7493</v>
+        <v>0.1363</v>
       </c>
       <c r="I16" t="n">
-        <v>1.2709</v>
+        <v>0.4184</v>
       </c>
       <c r="J16" t="n">
-        <v>0.8604000000000001</v>
+        <v>0.9149</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.363</v>
+        <v>0.9149</v>
       </c>
       <c r="L16" t="n">
-        <v>1.2234</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.3388</v>
+        <v>-0.3602</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.3863</v>
+        <v>-0.7786</v>
       </c>
       <c r="O16" t="n">
-        <v>0.0475</v>
+        <v>0.4184</v>
       </c>
       <c r="P16" t="n">
-        <v>0.616</v>
+        <v>0.2053</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.616</v>
+        <v>0.2053</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.0805</v>
+        <v>-0.3777</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.4534</v>
+        <v>-0.1976</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.6272</v>
+        <v>-0.1801</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.141</v>
+        <v>0.1327</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0125</v>
+        <v>0.1171</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1535</v>
+        <v>0.0156</v>
       </c>
       <c r="G17" t="n">
         <v>0.1918</v>
@@ -1780,13 +1780,13 @@
         <v>0.2053</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.5381</v>
+        <v>-0.2644</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.0659</v>
+        <v>0.0387</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.4722</v>
+        <v>-0.3031</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>G. KASANZI OBAMA</t>
+          <t>A. MONTERO ISLA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.209</v>
+        <v>-1.6949</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.2866</v>
+        <v>-0.5731000000000001</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.9224</v>
+        <v>-1.1218</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.829</v>
+        <v>-0.5185</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.2424</v>
+        <v>-1.2266</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.5866</v>
+        <v>0.7081</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.5698</v>
+        <v>1.5033</v>
       </c>
       <c r="K18" t="n">
-        <v>0.7855</v>
+        <v>0.9378</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.3552</v>
+        <v>0.5656</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.2592</v>
+        <v>-2.0218</v>
       </c>
       <c r="N18" t="n">
-        <v>-2.0279</v>
+        <v>-2.1643</v>
       </c>
       <c r="O18" t="n">
-        <v>0.7685999999999999</v>
+        <v>0.1425</v>
       </c>
       <c r="P18" t="n">
-        <v>1.0267</v>
+        <v>-0.616</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-2.0534</v>
       </c>
       <c r="R18" t="n">
-        <v>1.0267</v>
+        <v>1.4374</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.4067</v>
+        <v>-1.3899</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.7169</v>
+        <v>-0.8526</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.6899</v>
+        <v>-0.5374</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.8295</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.8295</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. MONTERO ISLA</t>
+          <t>G. KASANZI OBAMA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.3277</v>
+        <v>-2.0295</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.0961</v>
+        <v>-1.0774</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.2316</v>
+        <v>-0.9520999999999999</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.5185</v>
+        <v>-1.829</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.2266</v>
+        <v>-1.2424</v>
       </c>
       <c r="I19" t="n">
-        <v>0.7081</v>
+        <v>-0.5866</v>
       </c>
       <c r="J19" t="n">
-        <v>1.5033</v>
+        <v>-0.5698</v>
       </c>
       <c r="K19" t="n">
-        <v>0.9378</v>
+        <v>0.7855</v>
       </c>
       <c r="L19" t="n">
-        <v>0.5656</v>
+        <v>-1.3552</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.0218</v>
+        <v>-1.2592</v>
       </c>
       <c r="N19" t="n">
-        <v>-2.1643</v>
+        <v>-2.0279</v>
       </c>
       <c r="O19" t="n">
-        <v>0.1425</v>
+        <v>0.7685999999999999</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.616</v>
+        <v>1.0267</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.0534</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.4374</v>
+        <v>1.0267</v>
       </c>
       <c r="S19" t="n">
-        <v>-2.0228</v>
+        <v>-1.2272</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.3756</v>
+        <v>-0.5077</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.6472</v>
+        <v>-0.7195</v>
       </c>
       <c r="V19" t="n">
-        <v>0.8295</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0.8295</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.083</v>
+        <v>-3.0517</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.3164</v>
+        <v>-1.1071</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.7666</v>
+        <v>-1.9445</v>
       </c>
       <c r="G20" t="n">
         <v>-1.8564</v>
@@ -2014,13 +2014,13 @@
         <v>0.2053</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.4052</v>
+        <v>-0.3739</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3875</v>
+        <v>-0.1783</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0177</v>
+        <v>-0.1956</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. ABDULSALAM</t>
+          <t>C. HENDERSON</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.6813</v>
+        <v>-4.8135</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.0008</v>
+        <v>-2.4263</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.6805</v>
+        <v>-2.3872</v>
       </c>
       <c r="G21" t="n">
-        <v>0.6909999999999999</v>
+        <v>-2.0762</v>
       </c>
       <c r="H21" t="n">
-        <v>0.2143</v>
+        <v>-3.2472</v>
       </c>
       <c r="I21" t="n">
-        <v>0.4766</v>
+        <v>1.1709</v>
       </c>
       <c r="J21" t="n">
-        <v>1.6499</v>
+        <v>-0.141</v>
       </c>
       <c r="K21" t="n">
-        <v>1.5709</v>
+        <v>-1.1932</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0789</v>
+        <v>1.0522</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.9589</v>
+        <v>-1.9352</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.3566</v>
+        <v>-2.054</v>
       </c>
       <c r="O21" t="n">
-        <v>0.3977</v>
+        <v>0.1188</v>
       </c>
       <c r="P21" t="n">
-        <v>-2.4641</v>
+        <v>-2.0534</v>
       </c>
       <c r="Q21" t="n">
-        <v>-4.1068</v>
+        <v>-3.0801</v>
       </c>
       <c r="R21" t="n">
-        <v>1.6427</v>
+        <v>1.0267</v>
       </c>
       <c r="S21" t="n">
-        <v>0.4491</v>
+        <v>-0.6838</v>
       </c>
       <c r="T21" t="n">
-        <v>0.9141</v>
+        <v>-0.3837</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.465</v>
+        <v>-0.3001</v>
       </c>
       <c r="V21" t="n">
-        <v>-2.3573</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.4579</v>
+        <v>1.1786</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.8993</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>C. HENDERSON</t>
+          <t>M. ABDULSALAM</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.28</v>
+        <v>-5.0186</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.6941</v>
+        <v>-3.1515</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.586</v>
+        <v>-1.8671</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.0762</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="H22" t="n">
-        <v>-3.2472</v>
+        <v>0.2143</v>
       </c>
       <c r="I22" t="n">
-        <v>1.1709</v>
+        <v>0.4766</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.141</v>
+        <v>1.6499</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.1932</v>
+        <v>1.5709</v>
       </c>
       <c r="L22" t="n">
-        <v>1.0522</v>
+        <v>0.0789</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.9352</v>
+        <v>-0.9589</v>
       </c>
       <c r="N22" t="n">
-        <v>-2.054</v>
+        <v>-1.3566</v>
       </c>
       <c r="O22" t="n">
-        <v>0.1188</v>
+        <v>0.3977</v>
       </c>
       <c r="P22" t="n">
-        <v>-2.0534</v>
+        <v>-2.4641</v>
       </c>
       <c r="Q22" t="n">
-        <v>-3.0801</v>
+        <v>-4.1068</v>
       </c>
       <c r="R22" t="n">
-        <v>1.0267</v>
+        <v>1.6427</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1504</v>
+        <v>-0.8882</v>
       </c>
       <c r="T22" t="n">
-        <v>0.3485</v>
+        <v>-0.2365</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4988</v>
+        <v>-0.6516</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>-2.3573</v>
       </c>
       <c r="W22" t="n">
-        <v>1.1786</v>
+        <v>-0.4579</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.1786</v>
+        <v>-1.8993</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.67</v>
+        <v>-5.7014</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.9419</v>
+        <v>-4.1511</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.7282</v>
+        <v>-1.5503</v>
       </c>
       <c r="G23" t="n">
         <v>-2.1466</v>
@@ -2248,13 +2248,13 @@
         <v>0.8214</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.0244</v>
+        <v>-1.0558</v>
       </c>
       <c r="T23" t="n">
-        <v>0.1122</v>
+        <v>-0.097</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.1367</v>
+        <v>-0.9588</v>
       </c>
       <c r="V23" t="n">
         <v>-0.2402</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-7.8865</v>
+        <v>-7.707</v>
       </c>
       <c r="E24" t="n">
-        <v>-5.3908</v>
+        <v>-5.1816</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.4957</v>
+        <v>-2.5253</v>
       </c>
       <c r="G24" t="n">
         <v>-4.4418</v>
@@ -2326,13 +2326,13 @@
         <v>0.8214</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.1859</v>
+        <v>-1.0064</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.775</v>
+        <v>-0.5658</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.4109</v>
+        <v>-0.4406</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-8.922800000000001</v>
+        <v>-8.023199999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>-6.0762</v>
+        <v>-5.5532</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.8466</v>
+        <v>-2.47</v>
       </c>
       <c r="G25" t="n">
         <v>-4.9004</v>
@@ -2404,13 +2404,13 @@
         <v>1.2321</v>
       </c>
       <c r="S25" t="n">
-        <v>-2.1743</v>
+        <v>-1.2746</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.0462</v>
+        <v>-0.5232</v>
       </c>
       <c r="U25" t="n">
-        <v>-1.128</v>
+        <v>-0.7514</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-37.8212</v>
+        <v>-37.12430000000001</v>
       </c>
       <c r="E26" t="n">
-        <v>-21.6661</v>
+        <v>-21.666</v>
       </c>
       <c r="F26" t="n">
-        <v>-16.1554</v>
+        <v>-15.458</v>
       </c>
       <c r="G26" t="n">
         <v>-15.8098</v>
@@ -2479,16 +2479,16 @@
         <v>-19.5073</v>
       </c>
       <c r="R26" t="n">
-        <v>9.240300000000001</v>
+        <v>9.240299999999998</v>
       </c>
       <c r="S26" t="n">
-        <v>-9.9762</v>
+        <v>-9.278999999999998</v>
       </c>
       <c r="T26" t="n">
         <v>-3.6433</v>
       </c>
       <c r="U26" t="n">
-        <v>-6.333</v>
+        <v>-5.6357</v>
       </c>
       <c r="V26" t="n">
         <v>-1.768</v>
